--- a/Spec/haystacked_platform_config.xlsx
+++ b/Spec/haystacked_platform_config.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Platform Scope" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Basic Extraction Schema" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="NACE Codes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Unit Conversions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +43,9 @@
     </font>
     <font>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -69,12 +73,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12126,4 +12131,82 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Unit conversion rules for LLM-extracted values. Cross-industry — applies to all haystacked verticals. Tender Unit = canonical unit stored/expected. LLM Alias = unit LLM may emit instead. Factor = multiply LLM value to get Tender Unit. Detection Threshold = if LLM value exceeds this, assume wrong unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Tender Unit</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>LLM Alias</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Conversion Factor</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Detection Threshold</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aisle width, lift height: LLM may give mm instead of m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Spec/haystacked_platform_config.xlsx
+++ b/Spec/haystacked_platform_config.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -823,39 +823,39 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>is_agv_amr</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>true if document requests AGV, AMR, automated intralogistics vehicles, VNA robots, or self-driving warehouse/factory transport. true if words AGV, AMR, or VNA appear.</t>
+          <t>1-2 sentence summary of what is being procured and who the buyer is.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>null</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>missing_info</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -865,37 +865,10 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>1-2 sentence summary of what is being procured and who the buyer is.</t>
+          <t>List of important fields that cannot be determined from the document (e.g. ["lifting_height_mm", "aisle_width_mm"]).</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>missing_info</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>List of important fields that cannot be determined from the document (e.g. ["lifting_height_mm", "aisle_width_mm"]).</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/Spec/haystacked_platform_config.xlsx
+++ b/Spec/haystacked_platform_config.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -549,6 +549,11 @@
           <t>JSON Default</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Contact Fallback</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -634,7 +639,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>tender_date</t>
+          <t>deadline</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -649,19 +654,24 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Date the tender was issued. Extract in ANY format found; normalize output to DD.MM.YYYY.</t>
+          <t>Submission deadline. Extract in ANY format; normalize to DD.MM.YYYY.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>null</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>target</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>deadline</t>
+          <t>tender_date</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -676,12 +686,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Submission deadline. Extract in ANY format; normalize to DD.MM.YYYY.</t>
+          <t>Date the tender was issued. Extract in ANY format found; normalize output to DD.MM.YYYY.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>null</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>target</t>
         </is>
       </c>
     </row>
@@ -711,6 +726,11 @@
           <t>null</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -738,6 +758,11 @@
           <t>null</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -763,6 +788,11 @@
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t>null</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>trigger</t>
         </is>
       </c>
     </row>

--- a/Spec/haystacked_platform_config.xlsx
+++ b/Spec/haystacked_platform_config.xlsx
@@ -12189,23 +12189,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
       <c r="C3" t="n">
-        <v>0.001</v>
+        <v>1000</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aisle width, lift height: LLM may give mm instead of m</t>
+          <t>Aisle width, lift height: LLM may give meters instead of mm (OI-115b)</t>
         </is>
       </c>
     </row>
